--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,94 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,129 +442,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" t="n">
         <v>4</v>
       </c>
     </row>

--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,70 @@
         <v>4</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,14 @@
         <v>13</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,14 +560,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" t="n">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,158 @@
         <v>13</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/database/metric_dimensions.xlsx
+++ b/data/database/metric_dimensions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,62 @@
         <v>18</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
